--- a/Hospital_Management_System_HMS/HMS_DATA/AppData.xlsx
+++ b/Hospital_Management_System_HMS/HMS_DATA/AppData.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahan\git\repository\Hospital_Management_System_HMS\HMS_DATA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBC66F0-C155-4AE2-9C81-552C09C2BC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{488F3A9E-45CD-4020-A51E-D4CCF7C1C3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1780" yWindow="1780" windowWidth="14400" windowHeight="8710" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserData" sheetId="1" r:id="rId1"/>
@@ -21,7 +16,8 @@
     <sheet name="Patient4" sheetId="6" r:id="rId6"/>
     <sheet name="Patient5" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:K16"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -554,17 +550,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.46484375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,7 +583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -610,7 +606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -633,7 +629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -656,7 +652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -679,7 +675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -717,12 +713,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F48F780-9093-47E7-962A-32A88C22CFE5}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -730,7 +726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -738,7 +734,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -746,7 +742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -754,7 +750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -762,7 +758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
@@ -785,16 +781,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A75CAD9-A6DC-4EA1-B67B-CC70625CE4B4}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.53125" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +813,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -851,17 +847,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1DFB9D-B5BD-4525-9443-64B4971BCA2E}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -884,7 +880,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -918,18 +914,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A889174-AD1C-49B4-8F86-46035CD7BF5C}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -952,7 +948,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -986,18 +982,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B57403-7080-4617-AB05-270F9E339F61}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1020,7 +1016,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1054,18 +1050,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01ED607E-B04A-4BC9-9A0F-2890028E724A}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1084,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
